--- a/zzz_mod_info/project_info/ship_designer.xlsx
+++ b/zzz_mod_info/project_info/ship_designer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\Paradox Interactive\Hearts of Iron IV\mod\UTTNH Foxr Edition\zzz_mod_info\project_info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522965D0-C2D3-4304-A975-96946C274793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA29C3C4-5E07-41F7-8967-75446F47F441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{39E5E01B-E574-4484-8C70-F4508DC7758A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="78">
   <si>
     <t>中段</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -300,6 +300,14 @@
   </si>
   <si>
     <t>Island</t>
+  </si>
+  <si>
+    <t>水平装甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>垂直装甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -515,7 +523,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -540,6 +548,24 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -576,39 +602,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -930,26 +923,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="10"/>
-      <c r="J1" s="20" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="22"/>
+      <c r="J1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="19"/>
     </row>
     <row r="2" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -977,28 +970,28 @@
         <v>23</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="M2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1009,12 +1002,12 @@
       <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="13"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="25"/>
       <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
@@ -1022,76 +1015,76 @@
         <v>24</v>
       </c>
       <c r="I3" s="5"/>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L3" s="30" t="s">
+      <c r="L3" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="22" t="s">
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="Q3" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="12" t="s">
+      <c r="C4" s="26"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="24" t="s">
         <v>1</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="28" t="s">
+      <c r="J4" s="6"/>
+      <c r="K4" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="L4" s="33"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="28" t="s">
+      <c r="L4" s="14"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q4" s="25"/>
+      <c r="Q4" s="7"/>
     </row>
     <row r="5" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="15"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I5" s="5"/>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="21" t="s">
+      <c r="K5" s="9"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1099,46 +1092,46 @@
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="15"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="I6" s="5"/>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="20"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="21" t="s">
+      <c r="K6" s="9"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="18"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="30"/>
       <c r="H7" s="7"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="25"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="7"/>
     </row>
     <row r="8" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -1147,10 +1140,10 @@
       <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31"/>
       <c r="G8" s="4" t="s">
         <v>7</v>
       </c>
@@ -1158,20 +1151,20 @@
         <v>7</v>
       </c>
       <c r="I8" s="5"/>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K8" s="23" t="s">
+      <c r="K8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="35"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="23" t="s">
+      <c r="L8" s="16"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q8" s="21" t="s">
+      <c r="Q8" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1201,52 +1194,52 @@
         <v>2</v>
       </c>
       <c r="I9" s="5"/>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="K9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L9" s="21" t="s">
+      <c r="L9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="21" t="s">
+      <c r="M9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N9" s="21" t="s">
+      <c r="N9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="O9" s="21" t="s">
+      <c r="O9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P9" s="21" t="s">
+      <c r="P9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q9" s="21" t="s">
+      <c r="Q9" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
-      <c r="J10" s="20" t="s">
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
+      <c r="J10" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="27"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="19"/>
     </row>
     <row r="11" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -1273,28 +1266,28 @@
       <c r="H11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K11" s="21" t="s">
+      <c r="K11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L11" s="21" t="s">
+      <c r="L11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M11" s="22" t="s">
+      <c r="M11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="N11" s="22" t="s">
+      <c r="N11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="O11" s="21" t="s">
+      <c r="O11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P11" s="21" t="s">
+      <c r="P11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Q11" s="21" t="s">
+      <c r="Q11" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1305,86 +1298,86 @@
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="13"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="25"/>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="22" t="s">
+      <c r="K12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="30" t="s">
+      <c r="L12" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="32"/>
-      <c r="P12" s="22" t="s">
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="Q12" s="22" t="s">
+      <c r="Q12" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="12" t="s">
+      <c r="C13" s="26"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="24" t="s">
         <v>1</v>
       </c>
       <c r="H13" s="7"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="28" t="s">
+      <c r="J13" s="6"/>
+      <c r="K13" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="L13" s="33"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="28" t="s">
+      <c r="L13" s="14"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="7"/>
     </row>
     <row r="14" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="15"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="27"/>
       <c r="H14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K14" s="20"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="21" t="s">
+      <c r="K14" s="9"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1392,45 +1385,45 @@
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="15"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="27"/>
       <c r="H15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="21" t="s">
+      <c r="J15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K15" s="20"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="21" t="s">
+      <c r="K15" s="9"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="18"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="30"/>
       <c r="H16" s="7"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="25"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="7"/>
     </row>
     <row r="17" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
@@ -1439,30 +1432,30 @@
       <c r="B17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="19"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="31"/>
       <c r="G17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J17" s="21" t="s">
+      <c r="J17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K17" s="23" t="s">
+      <c r="K17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L17" s="35"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="23" t="s">
+      <c r="L17" s="16"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q17" s="21" t="s">
+      <c r="Q17" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1491,52 +1484,52 @@
       <c r="H18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J18" s="21" t="s">
+      <c r="J18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K18" s="21" t="s">
+      <c r="K18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L18" s="21" t="s">
+      <c r="L18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M18" s="21" t="s">
+      <c r="M18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N18" s="21" t="s">
+      <c r="N18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="O18" s="21" t="s">
+      <c r="O18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P18" s="21" t="s">
+      <c r="P18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q18" s="21" t="s">
+      <c r="Q18" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="10"/>
-      <c r="J19" s="20" t="s">
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22"/>
+      <c r="J19" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="27"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="19"/>
     </row>
     <row r="20" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1563,28 +1556,28 @@
       <c r="H20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J20" s="21" t="s">
+      <c r="J20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K20" s="21" t="s">
+      <c r="K20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L20" s="21" t="s">
+      <c r="L20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M20" s="22" t="s">
+      <c r="M20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="N20" s="22" t="s">
+      <c r="N20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="O20" s="21" t="s">
+      <c r="O20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P20" s="21" t="s">
+      <c r="P20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Q20" s="21" t="s">
+      <c r="Q20" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1595,86 +1588,86 @@
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="25"/>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="22" t="s">
+      <c r="J21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K21" s="22" t="s">
+      <c r="K21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L21" s="30" t="s">
+      <c r="L21" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M21" s="31"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="32"/>
-      <c r="P21" s="22" t="s">
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="Q21" s="22" t="s">
+      <c r="Q21" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="12" t="s">
+      <c r="C22" s="26"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="24" t="s">
         <v>1</v>
       </c>
       <c r="H22" s="7"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="28" t="s">
+      <c r="J22" s="6"/>
+      <c r="K22" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="L22" s="33"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="28" t="s">
+      <c r="L22" s="14"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q22" s="25"/>
+      <c r="Q22" s="7"/>
     </row>
     <row r="23" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="15"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="27"/>
       <c r="H23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="21" t="s">
+      <c r="J23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K23" s="20"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="21" t="s">
+      <c r="K23" s="9"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1682,45 +1675,45 @@
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="15"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="27"/>
       <c r="H24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J24" s="21" t="s">
+      <c r="J24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K24" s="20"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="21" t="s">
+      <c r="K24" s="9"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="18"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="30"/>
       <c r="H25" s="7"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="25"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="7"/>
     </row>
     <row r="26" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
@@ -1729,30 +1722,30 @@
       <c r="B26" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="31"/>
       <c r="G26" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J26" s="21" t="s">
+      <c r="J26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K26" s="23" t="s">
+      <c r="K26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L26" s="35"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="23" t="s">
+      <c r="L26" s="16"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q26" s="21" t="s">
+      <c r="Q26" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1781,52 +1774,52 @@
       <c r="H27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J27" s="21" t="s">
+      <c r="J27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K27" s="21" t="s">
+      <c r="K27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L27" s="21" t="s">
+      <c r="L27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M27" s="21" t="s">
+      <c r="M27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N27" s="21" t="s">
+      <c r="N27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="O27" s="21" t="s">
+      <c r="O27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P27" s="21" t="s">
+      <c r="P27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q27" s="21" t="s">
+      <c r="Q27" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="10"/>
-      <c r="J28" s="20" t="s">
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
+      <c r="J28" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="27"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="19"/>
     </row>
     <row r="29" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -1853,28 +1846,28 @@
       <c r="H29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J29" s="21" t="s">
+      <c r="J29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K29" s="21" t="s">
+      <c r="K29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L29" s="21" t="s">
+      <c r="L29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M29" s="22" t="s">
+      <c r="M29" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="N29" s="22" t="s">
+      <c r="N29" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="O29" s="21" t="s">
+      <c r="O29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P29" s="21" t="s">
+      <c r="P29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Q29" s="21" t="s">
+      <c r="Q29" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1885,86 +1878,86 @@
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="13"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="25"/>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J30" s="22" t="s">
+      <c r="J30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K30" s="22" t="s">
+      <c r="K30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L30" s="30" t="s">
+      <c r="L30" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="32"/>
-      <c r="P30" s="22" t="s">
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="Q30" s="22" t="s">
+      <c r="Q30" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="12" t="s">
+      <c r="C31" s="26"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="24" t="s">
         <v>1</v>
       </c>
       <c r="H31" s="7"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="28" t="s">
+      <c r="J31" s="6"/>
+      <c r="K31" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="L31" s="33"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="34"/>
-      <c r="P31" s="28" t="s">
+      <c r="L31" s="14"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q31" s="25"/>
+      <c r="Q31" s="7"/>
     </row>
     <row r="32" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="15"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="21" t="s">
+      <c r="J32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K32" s="20"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="34"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="21" t="s">
+      <c r="K32" s="9"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1972,45 +1965,45 @@
       <c r="A33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="15"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J33" s="21" t="s">
+      <c r="J33" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K33" s="20"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="21" t="s">
+      <c r="K33" s="9"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="18"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="30"/>
       <c r="H34" s="7"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="25"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="7"/>
     </row>
     <row r="35" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -2019,30 +2012,30 @@
       <c r="B35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="19"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="31"/>
       <c r="G35" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J35" s="21" t="s">
+      <c r="J35" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K35" s="23" t="s">
+      <c r="K35" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L35" s="35"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
-      <c r="O35" s="36"/>
-      <c r="P35" s="23" t="s">
+      <c r="L35" s="16"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q35" s="21" t="s">
+      <c r="Q35" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2071,52 +2064,52 @@
       <c r="H36" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J36" s="21" t="s">
+      <c r="J36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K36" s="21" t="s">
+      <c r="K36" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L36" s="21" t="s">
+      <c r="L36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M36" s="21" t="s">
+      <c r="M36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="N36" s="21" t="s">
+      <c r="N36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O36" s="21" t="s">
+      <c r="O36" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P36" s="21" t="s">
+      <c r="P36" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q36" s="21" t="s">
+      <c r="Q36" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="10"/>
-      <c r="J37" s="20" t="s">
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="22"/>
+      <c r="J37" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="27"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="19"/>
     </row>
     <row r="38" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -2143,28 +2136,28 @@
       <c r="H38" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J38" s="21" t="s">
+      <c r="J38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K38" s="21" t="s">
+      <c r="K38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L38" s="21" t="s">
+      <c r="L38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="M38" s="22" t="s">
+      <c r="M38" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N38" s="22" t="s">
+      <c r="N38" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="O38" s="21" t="s">
+      <c r="O38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="P38" s="21" t="s">
+      <c r="P38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Q38" s="21" t="s">
+      <c r="Q38" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2175,124 +2168,124 @@
       <c r="B39" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="13"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="25"/>
       <c r="G39" s="3" t="s">
         <v>45</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J39" s="22" t="s">
+      <c r="J39" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="K39" s="22" t="s">
+      <c r="K39" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="L39" s="30" t="s">
+      <c r="L39" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="32"/>
-      <c r="P39" s="22" t="s">
+      <c r="M39" s="12"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Q39" s="22" t="s">
+      <c r="Q39" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="11" t="s">
+      <c r="C40" s="26"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="23" t="s">
         <v>1</v>
       </c>
       <c r="H40" s="7"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="28" t="s">
+      <c r="J40" s="6"/>
+      <c r="K40" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="L40" s="33"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="20"/>
-      <c r="O40" s="34"/>
-      <c r="P40" s="28" t="s">
+      <c r="L40" s="14"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q40" s="25"/>
+      <c r="Q40" s="7"/>
     </row>
     <row r="41" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="14"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="26"/>
       <c r="H41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J41" s="21"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="34"/>
-      <c r="P41" s="20"/>
-      <c r="Q41" s="21" t="s">
+      <c r="J41" s="1"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="14"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="26"/>
       <c r="H42" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J42" s="21"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="34"/>
-      <c r="P42" s="20"/>
-      <c r="Q42" s="21" t="s">
+      <c r="J42" s="1"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="15"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="17"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="29"/>
       <c r="H43" s="7"/>
-      <c r="J43" s="24"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="33"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="34"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="25"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="15"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="7"/>
     </row>
     <row r="44" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -2301,30 +2294,30 @@
       <c r="B44" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="19"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="31"/>
       <c r="G44" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J44" s="21" t="s">
+      <c r="J44" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K44" s="23" t="s">
+      <c r="K44" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L44" s="35"/>
-      <c r="M44" s="29"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="36"/>
-      <c r="P44" s="23" t="s">
+      <c r="L44" s="16"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q44" s="21" t="s">
+      <c r="Q44" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2353,52 +2346,52 @@
       <c r="H45" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J45" s="21" t="s">
+      <c r="J45" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="K45" s="21" t="s">
+      <c r="K45" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L45" s="21" t="s">
+      <c r="L45" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M45" s="21" t="s">
+      <c r="M45" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="N45" s="21" t="s">
+      <c r="N45" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O45" s="21" t="s">
+      <c r="O45" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="P45" s="21" t="s">
+      <c r="P45" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q45" s="21" t="s">
+      <c r="Q45" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="10"/>
-      <c r="J46" s="20" t="s">
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="22"/>
+      <c r="J46" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="K46" s="26"/>
-      <c r="L46" s="26"/>
-      <c r="M46" s="26"/>
-      <c r="N46" s="26"/>
-      <c r="O46" s="26"/>
-      <c r="P46" s="26"/>
-      <c r="Q46" s="27"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="19"/>
     </row>
     <row r="47" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
@@ -2425,28 +2418,28 @@
       <c r="H47" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J47" s="21" t="s">
+      <c r="J47" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K47" s="21" t="s">
+      <c r="K47" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L47" s="21" t="s">
+      <c r="L47" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="M47" s="22" t="s">
+      <c r="M47" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N47" s="22" t="s">
+      <c r="N47" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="O47" s="21" t="s">
+      <c r="O47" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P47" s="21" t="s">
+      <c r="P47" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Q47" s="21" t="s">
+      <c r="Q47" s="1" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2457,86 +2450,86 @@
       <c r="B48" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="13"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="25"/>
       <c r="G48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J48" s="22" t="s">
+      <c r="J48" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="K48" s="22" t="s">
+      <c r="K48" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="L48" s="30" t="s">
+      <c r="L48" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M48" s="31"/>
-      <c r="N48" s="31"/>
-      <c r="O48" s="32"/>
-      <c r="P48" s="22" t="s">
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="13"/>
+      <c r="P48" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Q48" s="22" t="s">
+      <c r="Q48" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="14"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="12" t="s">
+      <c r="C49" s="26"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="24" t="s">
         <v>1</v>
       </c>
       <c r="H49" s="7"/>
-      <c r="J49" s="24"/>
-      <c r="K49" s="28" t="s">
+      <c r="J49" s="6"/>
+      <c r="K49" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="L49" s="33"/>
-      <c r="M49" s="20"/>
-      <c r="N49" s="20"/>
-      <c r="O49" s="34"/>
-      <c r="P49" s="28" t="s">
+      <c r="L49" s="14"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q49" s="25"/>
+      <c r="Q49" s="7"/>
     </row>
     <row r="50" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="15"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="27"/>
       <c r="H50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J50" s="21" t="s">
+      <c r="J50" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K50" s="20"/>
-      <c r="L50" s="33"/>
-      <c r="M50" s="20"/>
-      <c r="N50" s="20"/>
-      <c r="O50" s="34"/>
-      <c r="P50" s="20"/>
-      <c r="Q50" s="21" t="s">
+      <c r="K50" s="9"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="9"/>
+      <c r="O50" s="15"/>
+      <c r="P50" s="9"/>
+      <c r="Q50" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2544,77 +2537,77 @@
       <c r="A51" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="15"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="27"/>
       <c r="H51" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J51" s="21" t="s">
+      <c r="J51" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K51" s="20"/>
-      <c r="L51" s="33"/>
-      <c r="M51" s="20"/>
-      <c r="N51" s="20"/>
-      <c r="O51" s="34"/>
-      <c r="P51" s="20"/>
-      <c r="Q51" s="21" t="s">
+      <c r="K51" s="9"/>
+      <c r="L51" s="14"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="9"/>
+      <c r="Q51" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
-      <c r="B52" s="18"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="18"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="30"/>
       <c r="H52" s="7"/>
-      <c r="J52" s="24"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="33"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="20"/>
-      <c r="O52" s="34"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="25"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="9"/>
+      <c r="O52" s="15"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="7"/>
     </row>
     <row r="53" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="17"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="19"/>
+        <v>76</v>
+      </c>
+      <c r="C53" s="29"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="31"/>
       <c r="G53" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J53" s="21" t="s">
+      <c r="J53" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K53" s="23" t="s">
+      <c r="K53" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L53" s="35"/>
-      <c r="M53" s="29"/>
-      <c r="N53" s="29"/>
-      <c r="O53" s="36"/>
-      <c r="P53" s="23" t="s">
+      <c r="L53" s="16"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q53" s="21" t="s">
+      <c r="Q53" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2643,59 +2636,78 @@
       <c r="H54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J54" s="21" t="s">
+      <c r="J54" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K54" s="21" t="s">
+      <c r="K54" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L54" s="21" t="s">
+      <c r="L54" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M54" s="21" t="s">
+      <c r="M54" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N54" s="21" t="s">
+      <c r="N54" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="O54" s="21" t="s">
+      <c r="O54" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="P54" s="21" t="s">
+      <c r="P54" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q54" s="21" t="s">
+      <c r="Q54" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="10"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
-      <c r="M55" s="9"/>
-      <c r="N55" s="9"/>
-      <c r="O55" s="9"/>
-      <c r="P55" s="9"/>
-      <c r="Q55" s="10"/>
+      <c r="A55" s="20"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="22"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="21"/>
+      <c r="P55" s="21"/>
+      <c r="Q55" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="P31:P34"/>
-    <mergeCell ref="L48:O53"/>
-    <mergeCell ref="P22:P25"/>
-    <mergeCell ref="J37:Q37"/>
-    <mergeCell ref="P40:P43"/>
-    <mergeCell ref="P49:P52"/>
-    <mergeCell ref="K31:K34"/>
-    <mergeCell ref="L30:O35"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="C21:F26"/>
+    <mergeCell ref="C12:F17"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="G13:G16"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="C3:F8"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="G22:G25"/>
+    <mergeCell ref="C30:F35"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="G31:G34"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="C39:F44"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="G40:G43"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="J55:Q55"/>
+    <mergeCell ref="C48:F53"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="G49:G52"/>
+    <mergeCell ref="K49:K52"/>
     <mergeCell ref="J1:Q1"/>
     <mergeCell ref="J19:Q19"/>
     <mergeCell ref="J10:Q10"/>
@@ -2705,39 +2717,20 @@
     <mergeCell ref="L12:O17"/>
     <mergeCell ref="K4:K7"/>
     <mergeCell ref="P4:P7"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="J55:Q55"/>
-    <mergeCell ref="C48:F53"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="G49:G52"/>
-    <mergeCell ref="K49:K52"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="C39:F44"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="G40:G43"/>
+    <mergeCell ref="P13:P16"/>
+    <mergeCell ref="K13:K16"/>
+    <mergeCell ref="L21:O26"/>
+    <mergeCell ref="P31:P34"/>
+    <mergeCell ref="L48:O53"/>
+    <mergeCell ref="P22:P25"/>
+    <mergeCell ref="J37:Q37"/>
+    <mergeCell ref="P40:P43"/>
+    <mergeCell ref="P49:P52"/>
+    <mergeCell ref="K31:K34"/>
+    <mergeCell ref="L30:O35"/>
     <mergeCell ref="J46:Q46"/>
     <mergeCell ref="K40:K43"/>
     <mergeCell ref="L39:O44"/>
-    <mergeCell ref="P13:P16"/>
-    <mergeCell ref="K13:K16"/>
-    <mergeCell ref="L21:O26"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="G22:G25"/>
-    <mergeCell ref="C30:F35"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="G31:G34"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="C12:F17"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="G13:G16"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="C3:F8"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="C21:F26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
